--- a/WorkBot/main/data/orders/Sysco/Sysco_Bakery_20260826.xlsx
+++ b/WorkBot/main/data/orders/Sysco/Sysco_Bakery_20260826.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1193,6 +1193,27 @@
         <v>147.32</v>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>7119250</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Naked - Mighty Mango</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" t="n">
+        <v>26.89</v>
+      </c>
+      <c r="E40" t="n">
+        <v>26.89</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
